--- a/ig/ch-vacd/StructureDefinition-ch-vacd-recommendation-request-message.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-recommendation-request-message.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$441</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14621" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15761" uniqueCount="787">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2311,6 +2311,112 @@
   </si>
   <si>
     <t>Bundle.entry:Observation.response.outcome</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation</t>
+  </si>
+  <si>
+    <t>TravelInformation</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition {http://fhir.ch/ig/ch-vacd/StructureDefinition/ch-vacd-travel-information}
+</t>
+  </si>
+  <si>
+    <t>Detailed information about conditions, problems or diagnoses</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:TravelInformation.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -2650,7 +2756,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN409"/>
+  <dimension ref="A1:AN441"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="true" bestFit="true"/>
@@ -48925,9 +49031,11 @@
         <v>746</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="C409" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="C409" t="s" s="2">
+        <v>747</v>
+      </c>
       <c r="D409" t="s" s="2">
         <v>78</v>
       </c>
@@ -48936,7 +49044,7 @@
         <v>79</v>
       </c>
       <c r="G409" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H409" t="s" s="2">
         <v>78</v>
@@ -48948,20 +49056,16 @@
         <v>89</v>
       </c>
       <c r="K409" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L409" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="L409" t="s" s="2">
-        <v>748</v>
-      </c>
       <c r="M409" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="N409" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="O409" t="s" s="2">
-        <v>751</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N409" s="2"/>
+      <c r="O409" s="2"/>
       <c r="P409" t="s" s="2">
         <v>78</v>
       </c>
@@ -49009,35 +49113,3661 @@
         <v>78</v>
       </c>
       <c r="AF409" t="s" s="2">
-        <v>746</v>
+        <v>233</v>
       </c>
       <c r="AG409" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH409" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI409" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ409" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AK409" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL409" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM409" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN409" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="410" hidden="true">
+      <c r="A410" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B410" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C410" s="2"/>
+      <c r="D410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E410" s="2"/>
+      <c r="F410" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G410" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K410" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L410" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M410" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N410" s="2"/>
+      <c r="O410" s="2"/>
+      <c r="P410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q410" s="2"/>
+      <c r="R410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF410" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG410" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH410" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL410" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM410" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN410" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="411" hidden="true">
+      <c r="A411" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B411" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C411" s="2"/>
+      <c r="D411" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E411" s="2"/>
+      <c r="F411" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G411" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K411" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L411" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M411" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N411" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O411" s="2"/>
+      <c r="P411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q411" s="2"/>
+      <c r="R411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF411" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG411" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH411" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ411" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL411" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM411" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN411" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="412" hidden="true">
+      <c r="A412" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B412" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C412" s="2"/>
+      <c r="D412" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E412" s="2"/>
+      <c r="F412" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G412" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I412" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J412" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K412" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L412" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M412" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N412" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O412" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q412" s="2"/>
+      <c r="R412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF412" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG412" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH412" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ412" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL412" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM412" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN412" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="413" hidden="true">
+      <c r="A413" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B413" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C413" s="2"/>
+      <c r="D413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E413" s="2"/>
+      <c r="F413" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G413" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J413" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L413" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M413" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N413" s="2"/>
+      <c r="O413" s="2"/>
+      <c r="P413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q413" s="2"/>
+      <c r="R413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF413" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG413" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH413" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ413" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK409" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL409" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM409" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN409" t="s" s="2">
+      <c r="AK413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM413" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN413" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="414" hidden="true">
+      <c r="A414" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B414" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C414" s="2"/>
+      <c r="D414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E414" s="2"/>
+      <c r="F414" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G414" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J414" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K414" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L414" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M414" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N414" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O414" s="2"/>
+      <c r="P414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q414" s="2"/>
+      <c r="R414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF414" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG414" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH414" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ414" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM414" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN414" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="415" hidden="true">
+      <c r="A415" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B415" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C415" s="2"/>
+      <c r="D415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E415" s="2"/>
+      <c r="F415" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G415" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K415" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="L415" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="M415" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N415" s="2"/>
+      <c r="O415" s="2"/>
+      <c r="P415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q415" s="2"/>
+      <c r="R415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF415" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG415" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH415" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK415" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL415" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM415" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN415" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="416" hidden="true">
+      <c r="A416" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B416" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C416" s="2"/>
+      <c r="D416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E416" s="2"/>
+      <c r="F416" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G416" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J416" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K416" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L416" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M416" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N416" s="2"/>
+      <c r="O416" s="2"/>
+      <c r="P416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q416" s="2"/>
+      <c r="R416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF416" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG416" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH416" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI416" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AJ416" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM416" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN416" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="417" hidden="true">
+      <c r="A417" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B417" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C417" s="2"/>
+      <c r="D417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E417" s="2"/>
+      <c r="F417" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G417" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K417" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L417" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M417" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N417" s="2"/>
+      <c r="O417" s="2"/>
+      <c r="P417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q417" s="2"/>
+      <c r="R417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF417" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG417" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH417" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL417" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM417" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN417" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="418" hidden="true">
+      <c r="A418" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B418" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C418" s="2"/>
+      <c r="D418" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E418" s="2"/>
+      <c r="F418" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G418" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K418" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L418" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M418" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N418" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O418" s="2"/>
+      <c r="P418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q418" s="2"/>
+      <c r="R418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF418" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG418" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH418" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ418" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL418" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM418" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN418" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="419" hidden="true">
+      <c r="A419" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B419" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C419" s="2"/>
+      <c r="D419" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E419" s="2"/>
+      <c r="F419" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G419" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I419" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J419" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K419" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L419" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M419" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N419" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O419" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q419" s="2"/>
+      <c r="R419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF419" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG419" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH419" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ419" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL419" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM419" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN419" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="420" hidden="true">
+      <c r="A420" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B420" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C420" s="2"/>
+      <c r="D420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E420" s="2"/>
+      <c r="F420" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G420" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J420" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K420" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L420" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M420" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N420" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O420" s="2"/>
+      <c r="P420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q420" s="2"/>
+      <c r="R420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X420" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="Y420" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z420" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AA420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF420" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG420" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH420" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ420" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM420" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN420" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="421" hidden="true">
+      <c r="A421" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B421" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C421" s="2"/>
+      <c r="D421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E421" s="2"/>
+      <c r="F421" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G421" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J421" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K421" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L421" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M421" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N421" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O421" s="2"/>
+      <c r="P421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q421" s="2"/>
+      <c r="R421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF421" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AG421" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH421" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ421" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM421" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN421" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="422" hidden="true">
+      <c r="A422" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="B422" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C422" s="2"/>
+      <c r="D422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E422" s="2"/>
+      <c r="F422" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G422" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J422" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K422" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L422" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M422" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="N422" s="2"/>
+      <c r="O422" s="2"/>
+      <c r="P422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q422" s="2"/>
+      <c r="R422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF422" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG422" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH422" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI422" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AJ422" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM422" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN422" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="423" hidden="true">
+      <c r="A423" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="B423" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C423" s="2"/>
+      <c r="D423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E423" s="2"/>
+      <c r="F423" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G423" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K423" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L423" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M423" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N423" s="2"/>
+      <c r="O423" s="2"/>
+      <c r="P423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q423" s="2"/>
+      <c r="R423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF423" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG423" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH423" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL423" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM423" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN423" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="424" hidden="true">
+      <c r="A424" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B424" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C424" s="2"/>
+      <c r="D424" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E424" s="2"/>
+      <c r="F424" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G424" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K424" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L424" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M424" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N424" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O424" s="2"/>
+      <c r="P424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q424" s="2"/>
+      <c r="R424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF424" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG424" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH424" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ424" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL424" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM424" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN424" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="425" hidden="true">
+      <c r="A425" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B425" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="C425" s="2"/>
+      <c r="D425" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E425" s="2"/>
+      <c r="F425" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G425" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I425" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J425" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K425" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L425" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M425" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N425" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O425" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q425" s="2"/>
+      <c r="R425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF425" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG425" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH425" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ425" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL425" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM425" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN425" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="426" hidden="true">
+      <c r="A426" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B426" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C426" s="2"/>
+      <c r="D426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E426" s="2"/>
+      <c r="F426" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G426" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J426" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K426" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L426" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M426" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N426" s="2"/>
+      <c r="O426" s="2"/>
+      <c r="P426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q426" s="2"/>
+      <c r="R426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X426" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="Y426" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="Z426" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF426" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG426" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH426" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ426" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM426" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN426" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="427" hidden="true">
+      <c r="A427" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="B427" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C427" s="2"/>
+      <c r="D427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E427" s="2"/>
+      <c r="F427" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G427" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J427" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K427" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L427" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M427" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N427" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O427" s="2"/>
+      <c r="P427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q427" s="2"/>
+      <c r="R427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF427" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG427" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH427" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ427" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM427" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN427" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="428" hidden="true">
+      <c r="A428" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B428" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C428" s="2"/>
+      <c r="D428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E428" s="2"/>
+      <c r="F428" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G428" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J428" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K428" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L428" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M428" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N428" s="2"/>
+      <c r="O428" s="2"/>
+      <c r="P428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q428" s="2"/>
+      <c r="R428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF428" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG428" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH428" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ428" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM428" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN428" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="429" hidden="true">
+      <c r="A429" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C429" s="2"/>
+      <c r="D429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E429" s="2"/>
+      <c r="F429" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G429" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J429" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K429" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L429" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M429" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N429" s="2"/>
+      <c r="O429" s="2"/>
+      <c r="P429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q429" s="2"/>
+      <c r="R429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF429" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AG429" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH429" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ429" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM429" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN429" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="430" hidden="true">
+      <c r="A430" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C430" s="2"/>
+      <c r="D430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E430" s="2"/>
+      <c r="F430" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G430" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J430" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K430" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L430" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M430" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N430" s="2"/>
+      <c r="O430" s="2"/>
+      <c r="P430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q430" s="2"/>
+      <c r="R430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF430" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG430" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH430" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ430" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM430" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN430" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="431" hidden="true">
+      <c r="A431" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B431" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C431" s="2"/>
+      <c r="D431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E431" s="2"/>
+      <c r="F431" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G431" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J431" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K431" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L431" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M431" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N431" s="2"/>
+      <c r="O431" s="2"/>
+      <c r="P431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q431" s="2"/>
+      <c r="R431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF431" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG431" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH431" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ431" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM431" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN431" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="432" hidden="true">
+      <c r="A432" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="B432" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C432" s="2"/>
+      <c r="D432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E432" s="2"/>
+      <c r="F432" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G432" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J432" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K432" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L432" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M432" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N432" s="2"/>
+      <c r="O432" s="2"/>
+      <c r="P432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q432" s="2"/>
+      <c r="R432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF432" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG432" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH432" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI432" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AJ432" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM432" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN432" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="433" hidden="true">
+      <c r="A433" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B433" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C433" s="2"/>
+      <c r="D433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E433" s="2"/>
+      <c r="F433" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G433" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K433" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L433" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M433" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N433" s="2"/>
+      <c r="O433" s="2"/>
+      <c r="P433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q433" s="2"/>
+      <c r="R433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF433" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG433" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH433" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL433" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM433" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN433" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="434" hidden="true">
+      <c r="A434" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B434" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C434" s="2"/>
+      <c r="D434" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E434" s="2"/>
+      <c r="F434" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G434" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K434" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L434" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M434" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N434" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O434" s="2"/>
+      <c r="P434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q434" s="2"/>
+      <c r="R434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF434" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG434" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH434" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ434" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL434" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="AM434" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN434" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="435" hidden="true">
+      <c r="A435" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B435" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C435" s="2"/>
+      <c r="D435" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E435" s="2"/>
+      <c r="F435" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G435" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I435" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J435" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K435" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L435" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M435" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N435" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O435" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="P435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q435" s="2"/>
+      <c r="R435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF435" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG435" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH435" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ435" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL435" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM435" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN435" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="436" hidden="true">
+      <c r="A436" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="B436" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C436" s="2"/>
+      <c r="D436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E436" s="2"/>
+      <c r="F436" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G436" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J436" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K436" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L436" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M436" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N436" s="2"/>
+      <c r="O436" s="2"/>
+      <c r="P436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q436" s="2"/>
+      <c r="R436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF436" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG436" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH436" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ436" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM436" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN436" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="437" hidden="true">
+      <c r="A437" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="B437" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C437" s="2"/>
+      <c r="D437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E437" s="2"/>
+      <c r="F437" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G437" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J437" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K437" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L437" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M437" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="N437" s="2"/>
+      <c r="O437" s="2"/>
+      <c r="P437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q437" s="2"/>
+      <c r="R437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF437" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG437" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH437" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ437" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM437" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN437" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="438" hidden="true">
+      <c r="A438" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="B438" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C438" s="2"/>
+      <c r="D438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E438" s="2"/>
+      <c r="F438" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G438" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J438" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K438" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L438" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M438" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N438" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O438" s="2"/>
+      <c r="P438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q438" s="2"/>
+      <c r="R438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF438" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG438" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH438" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ438" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM438" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN438" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="439" hidden="true">
+      <c r="A439" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="B439" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C439" s="2"/>
+      <c r="D439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E439" s="2"/>
+      <c r="F439" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G439" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J439" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K439" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L439" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M439" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N439" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O439" s="2"/>
+      <c r="P439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q439" s="2"/>
+      <c r="R439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF439" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG439" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH439" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ439" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM439" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN439" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="440" hidden="true">
+      <c r="A440" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B440" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C440" s="2"/>
+      <c r="D440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E440" s="2"/>
+      <c r="F440" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G440" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J440" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K440" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L440" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M440" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N440" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O440" s="2"/>
+      <c r="P440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q440" s="2"/>
+      <c r="R440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF440" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG440" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH440" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM440" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN440" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="441" hidden="true">
+      <c r="A441" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B441" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C441" s="2"/>
+      <c r="D441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E441" s="2"/>
+      <c r="F441" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G441" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J441" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K441" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="L441" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="M441" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="N441" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O441" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="P441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q441" s="2"/>
+      <c r="R441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF441" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="AG441" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH441" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ441" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM441" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN441" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN409">
+  <autoFilter ref="A1:AN441">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -49047,7 +52777,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI408">
+  <conditionalFormatting sqref="A2:AI440">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
